--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R2" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R3" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R4" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R5" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R6" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1187,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1308,12 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R7" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1378,19 +1298,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1434,12 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R8" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1504,19 +1409,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1560,12 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R9" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1630,19 +1520,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1686,12 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R10" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1756,19 +1631,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1812,12 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R11" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1882,19 +1742,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1938,12 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1975,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444713.1513234376</v>
+        <v>444713</v>
       </c>
       <c r="R12" t="n">
-        <v>6392779.643184017</v>
+        <v>6392780</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2008,19 +1853,9 @@
           <t>1974-01-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110774</v>
+        <v>110779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101914</v>
+        <v>101919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110779</v>
+        <v>110787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101919</v>
+        <v>101927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982895</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74470399</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553452</v>
       </c>
       <c r="B4" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74574017</v>
       </c>
       <c r="B5" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>74552688</v>
       </c>
       <c r="B6" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>74561001</v>
       </c>
       <c r="B7" t="n">
-        <v>101736</v>
+        <v>101746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>74767514</v>
       </c>
       <c r="B8" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>74770311</v>
       </c>
       <c r="B9" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>74857200</v>
       </c>
       <c r="B10" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>74948066</v>
       </c>
       <c r="B11" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>75151559</v>
       </c>
       <c r="B12" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74553452</v>
+        <v>74499990</v>
       </c>
       <c r="B4" t="n">
-        <v>107084</v>
+        <v>97534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,23 +908,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219686</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,7 +968,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathraea squamaria. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Huperzia selago. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,27 +1004,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74574017</v>
+        <v>74553452</v>
       </c>
       <c r="B5" t="n">
-        <v>109316</v>
+        <v>107084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>219686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Leontodon hispidus. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathraea squamaria. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,32 +1115,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74552688</v>
+        <v>74574017</v>
       </c>
       <c r="B6" t="n">
-        <v>101762</v>
+        <v>109316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>220228</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus vernus. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Leontodon hispidus. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,27 +1226,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74561001</v>
+        <v>74552688</v>
       </c>
       <c r="B7" t="n">
-        <v>101746</v>
+        <v>101762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221223</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus niger. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus vernus. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74767514</v>
+        <v>74561001</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>101746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219875</v>
+        <v>221223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,7 +1412,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus niger. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74770311</v>
+        <v>74767514</v>
       </c>
       <c r="B9" t="n">
-        <v>98703</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>219875</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,7 +1523,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera bifolia. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74857200</v>
+        <v>74770311</v>
       </c>
       <c r="B10" t="n">
-        <v>105732</v>
+        <v>98703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1638,7 +1634,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Pyrola chlorantha. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera bifolia. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74948066</v>
+        <v>74857200</v>
       </c>
       <c r="B11" t="n">
-        <v>110797</v>
+        <v>105732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,7 +1745,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Sanicula europaea. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Pyrola chlorantha. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,32 +1781,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>75151559</v>
+        <v>74948066</v>
       </c>
       <c r="B12" t="n">
-        <v>101937</v>
+        <v>110797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221317</v>
+        <v>219711</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,7 +1856,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Trifolium aureum. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Sanicula europaea. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,6 +1885,117 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>75151559</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101937</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6392780</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Trifolium aureum. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ängsmark ovan brant</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982895</v>
+        <v>74553452</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>107608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>219686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Hypochoeris maculata. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathraea squamaria. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74470399</v>
+        <v>74948066</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>111389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Hepatica nobilis. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Sanicula europaea. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74499990</v>
+        <v>74770311</v>
       </c>
       <c r="B4" t="n">
-        <v>97534</v>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,19 +908,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Huperzia selago. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera bifolia. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74553452</v>
+        <v>2962821</v>
       </c>
       <c r="B5" t="n">
-        <v>107084</v>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>219875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+          <t>Bergsledet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>444713</v>
       </c>
       <c r="R5" t="n">
-        <v>6392780</v>
+        <v>6392850</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,17 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1974-01-01</t>
+          <t>1999-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathraea squamaria. LEG: Roland Carlsson</t>
+          <t>1999-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,54 +1092,50 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ängsmark ovan brant</t>
+          <t>Ängsmark i skog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74574017</v>
+        <v>74767514</v>
       </c>
       <c r="B6" t="n">
-        <v>109316</v>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>219875</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,7 +1185,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Leontodon hispidus. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1221,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74552688</v>
+        <v>73982895</v>
       </c>
       <c r="B7" t="n">
-        <v>101762</v>
+        <v>109814</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>220204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,7 +1296,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus vernus. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Hypochoeris maculata. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74561001</v>
+        <v>74574017</v>
       </c>
       <c r="B8" t="n">
-        <v>101746</v>
+        <v>109865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>220228</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,7 +1407,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus niger. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Leontodon hispidus. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,48 +1443,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74767514</v>
+        <v>2582254</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>110078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+          <t>Bergsledet, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>444713</v>
       </c>
       <c r="R9" t="n">
-        <v>6392780</v>
+        <v>6392850</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,17 +1508,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1974-01-01</t>
+          <t>1999-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
+          <t>1999-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,70 +1527,66 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Ängsmark ovan brant</t>
+          <t>Ängsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74770311</v>
+        <v>3411668</v>
       </c>
       <c r="B10" t="n">
-        <v>98703</v>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+          <t>Tabergs södra industriområde, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444713</v>
+        <v>444561</v>
       </c>
       <c r="R10" t="n">
-        <v>6392780</v>
+        <v>6392928</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,17 +1610,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1974-01-01</t>
+          <t>1999-06-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1974-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Platanthera bifolia. LEG: Roland Carlsson</t>
+          <t>1999-06-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1629,28 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Ängsmark ovan brant</t>
+          <t>Kulturmark,vägren</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>74857200</v>
       </c>
       <c r="B11" t="n">
-        <v>105732</v>
+        <v>106243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,32 +1758,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74948066</v>
+        <v>74561001</v>
       </c>
       <c r="B12" t="n">
-        <v>110797</v>
+        <v>102224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219711</v>
+        <v>221223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,7 +1833,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Sanicula europaea. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus niger. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>75151559</v>
+        <v>74552688</v>
       </c>
       <c r="B13" t="n">
-        <v>101937</v>
+        <v>102240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1880,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221317</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,7 +1944,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Trifolium aureum. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Lathyrus vernus. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,6 +1977,433 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>75151559</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102418</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6392780</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Trifolium aureum. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ängsmark ovan brant</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74499990</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6392780</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Huperzia selago. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ängsmark ovan brant</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74470399</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kåperyd. 400m VSV Kåperyd, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6392780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D9j 0616. SOM: Hepatica nobilis. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ängsmark ovan brant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6733558</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergsledet, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>444713</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6392850</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Månsarp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1999-06-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1999-06-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Ängsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35569-2025 artfynd.xlsx
+++ b/artfynd/A 35569-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74553452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74948066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770311</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2962821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74767514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982895</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74574017</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2582254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3411668</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74857200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74561001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2088,6 +2153,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75151559</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74499990</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2306,6 +2381,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74470399</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,8 +2484,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6733558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>